--- a/NRCS/Requirements/NRCS_information_New.xlsx
+++ b/NRCS/Requirements/NRCS_information_New.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanwin/Documents/GitHub/School_TimeTable/NRCS/Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E2ADEF-B110-5747-A57C-ECEC342B606A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2887E1-D297-C940-9EFF-5D7292F56C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28800" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{185E7927-55DF-B544-BA77-C3C9E03ED088}"/>
   </bookViews>
@@ -1083,7 +1083,7 @@
         <v>7</v>
       </c>
       <c r="M7" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -1247,7 +1247,7 @@
         <v>3</v>
       </c>
       <c r="M11" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
